--- a/Albanian Municipalities.xlsx
+++ b/Albanian Municipalities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Transparency Radar Albania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65ACD6F1-57FC-4A7D-9BA5-36C16277B003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165C1DB8-543B-4B38-91DE-4E68FFF0836D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="167">
   <si>
     <t>No.</t>
   </si>
@@ -501,9 +501,6 @@
   </si>
   <si>
     <t>https://bashkiaberat.gov.al/</t>
-  </si>
-  <si>
-    <t>Unsafe Error, Not Secure, Servers down!</t>
   </si>
   <si>
     <t>ERROR</t>
@@ -1202,16 +1199,16 @@
         <v>20</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E8" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -1514,9 +1511,6 @@
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>160</v>
-      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
@@ -2004,9 +1998,6 @@
       </c>
       <c r="F45" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
@@ -2496,7 +2487,7 @@
         <v>127</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2504,7 +2495,7 @@
         <v>128</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -2512,7 +2503,7 @@
         <v>129</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -2520,7 +2511,7 @@
         <v>128</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
